--- a/resultados/vitorino/erros_varredura.xlsx
+++ b/resultados/vitorino/erros_varredura.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,7 +461,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -472,7 +472,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-31 13:00:32</t>
+          <t>2026-07-31 13:02:33</t>
         </is>
       </c>
     </row>
@@ -484,23 +484,79 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.vitorino.pr.gov.br/</t>
+          <t>https://vitorino.pr.gov.br/c/noticias/</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D3" t="n">
+        <v>404</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-07-31 22:13:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>vitorino</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://www.portalcr2.com.br/convenio-tranf-voluntaria/transferencias-voluntarias-vitorino</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-07-31 13:02:33</t>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-07-31 22:20:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>vitorino</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://www.vitorino.pr.gov.br/Conteudo?data=234430cc83d7ba87d23f713568dabedd</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>404</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-07-31 22:27:17</t>
         </is>
       </c>
     </row>
